--- a/content/tz-eda-na-kitayskom-yazyke.xlsx
+++ b/content/tz-eda-na-kitayskom-yazyke.xlsx
@@ -661,7 +661,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Гастрономический словарь Китая: 60 слов, без которых не разобраться в меню</t>
+          <t>Еда на китайском: 60 слов, без которых не разобраться в меню</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Гастрономический словарь Китая: 60 слов, без которых не разобраться в меню</t>
+          <t>Еда на китайском: 60 слов, без которых не разобраться в меню</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Гастрономический словарь Китая: 60 слов, без которых не разобраться в меню</t>
+          <t>Еда на китайском: 60 слов, без которых не разобраться в меню</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">

--- a/content/tz-eda-na-kitayskom-yazyke.xlsx
+++ b/content/tz-eda-na-kitayskom-yazyke.xlsx
@@ -1760,22 +1760,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>啤酒</t>
+          <t>果汁</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>píjiǔ</t>
+          <t>guǒzhī</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>пиво</t>
+          <t>сок</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>酒 — знак всех спиртных напитков</t>
+          <t>果 «плод» + 汁 «сок»; 苹果汁 — яблочный</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>В Чэнду я выбрала блюдо со знаком 煮 «варить в воде» — 水煮鱼 — и ждала диетический ужин. Принесли таз: палец красного масла, слой сушёного перца и где-то на дне рыба. Оказалось, 水煮 в сычуаньской кухне давно не значит «сварено в воде». Урок: формула работает почти всегда, но у регионов есть свои устойчивые сочетания. И фразу 不要辣 лучше выучить до поездки, а не после.</t>
+          <t>В Чэнду я выбрала блюдо со знаком 煮 «варить в воде» — 水煮鱼 — и ждала диетический ужин. Принесли таз: слой красного масла толщиной в палец, горка сушёного перца и где-то на дне рыба. Оказалось, 水煮 в сычуаньской кухне давно не значит «сварено в воде». Урок: формула работает почти всегда, но у регионов есть свои устойчивые сочетания. И фразу 不要辣 лучше выучить до поездки, а не после.</t>
         </is>
       </c>
     </row>
